--- a/backend/Data_Dictionary_v3.xlsx
+++ b/backend/Data_Dictionary_v3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\30. Open Source llm -RAG\PubSec-Info-Assistant-Offshore\backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{734B7B57-D739-4C93-9579-3F8BF5D8A238}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{078E0543-5A27-4FFE-BA86-432CEB44A4C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -258,36 +258,24 @@
     <t>sakani_beneficiary_price_max</t>
   </si>
   <si>
-    <t>Maximum Price for Sakani beneficiaries. Example: 267922.798</t>
-  </si>
-  <si>
     <t>non_sakani_beneficiary_price_min</t>
   </si>
   <si>
     <t>non_sakani_beneficiary_price_max</t>
   </si>
   <si>
-    <t>Maximum Price for non-Sakani beneficiaries. Example: 330190</t>
-  </si>
-  <si>
     <t>apartment_area_meter_min</t>
   </si>
   <si>
     <t>apartment_area_meter_max</t>
   </si>
   <si>
-    <t>Maximum Area of the apartment in square meters. Example: 152.5</t>
-  </si>
-  <si>
     <t>living_area_min</t>
   </si>
   <si>
     <t>living_area_max</t>
   </si>
   <si>
-    <t>Maximum Size of the living area in square meters. Example: 19.76</t>
-  </si>
-  <si>
     <t>Available Floor numbers of the unit. Example: 2,6</t>
   </si>
   <si>
@@ -297,39 +285,24 @@
     <t>bathroom_count_max</t>
   </si>
   <si>
-    <t>Maximum Number of bathrooms in the unit. Example: 4</t>
-  </si>
-  <si>
-    <t>Minimum Number of bathrooms in the unit. Example: 2</t>
-  </si>
-  <si>
     <t>number_of_rooms_min</t>
   </si>
   <si>
     <t>number_of_rooms_max</t>
   </si>
   <si>
-    <t>Maximum Total number of rooms in the unit. Example: 3</t>
-  </si>
-  <si>
     <t>master_bedroom_size_min</t>
   </si>
   <si>
     <t>master_bedroom_size_max</t>
   </si>
   <si>
-    <t>Maximum Size of the master bedroom in square meters. Example: 18.7</t>
-  </si>
-  <si>
     <t>living_room_size_min</t>
   </si>
   <si>
     <t>living_room_size_max</t>
   </si>
   <si>
-    <t>Maximum Size of the living room in square meters. Example: 16</t>
-  </si>
-  <si>
     <t>kitchen_size_min</t>
   </si>
   <si>
@@ -342,39 +315,6 @@
     <t>guestroom_size_max</t>
   </si>
   <si>
-    <t>Maximum Size of the kitchen in square meters. Example: 8.8</t>
-  </si>
-  <si>
-    <t>Maximum Size of the guestroom in square meters. Example: 23</t>
-  </si>
-  <si>
-    <t>Minimum Size of the guestroom in square meters. Example: 18</t>
-  </si>
-  <si>
-    <t>Minimum Size of the kitchen in square meters. Example: 7.2</t>
-  </si>
-  <si>
-    <t>Minimum Size of the living room in square meters. Example: 13</t>
-  </si>
-  <si>
-    <t>Minimum Size of the master bedroom in square meters. Example: 16.5</t>
-  </si>
-  <si>
-    <t>Minimum Total number of rooms in the unit. Example: 1</t>
-  </si>
-  <si>
-    <t>Minimum Size of the living area in square meters. Example: 15.78</t>
-  </si>
-  <si>
-    <t>Minimum Area of the apartment in square meters. Example: 149.1</t>
-  </si>
-  <si>
-    <t>Minimum Price for non-Sakani beneficiaries. Example: 301921</t>
-  </si>
-  <si>
-    <t>Minimum Price for Sakani beneficiaries. Example: 246222.652</t>
-  </si>
-  <si>
     <t>Name of city where project is located. Example: Mecca</t>
   </si>
   <si>
@@ -406,6 +346,66 @@
   </si>
   <si>
     <t>Size of the living area in square meters. Example: 15.78</t>
+  </si>
+  <si>
+    <t>Maximum number of rooms in the project. Example: 3</t>
+  </si>
+  <si>
+    <t>The minimum size of the master bedroom in square meters across the projects, for example, is 16.5.</t>
+  </si>
+  <si>
+    <t>The maximum size of the master bedroom in square meters across the projects, for example, is 18.7.</t>
+  </si>
+  <si>
+    <t>The minimum size of the living room in square meters across the projects, for example, is 13.</t>
+  </si>
+  <si>
+    <t>The maximum size of the living room in square meters across the projects, for example, is 16.</t>
+  </si>
+  <si>
+    <t>The minimum size of the kitchen in square meters across the projects, for example, is 7.2.</t>
+  </si>
+  <si>
+    <t>The maximum size of the kitchen in square meters across the projects, for example, is 8.8.</t>
+  </si>
+  <si>
+    <t>The minimum size of the guest room in square meters across the projects, for example, is 18.</t>
+  </si>
+  <si>
+    <t>The maximum size of the guest room in square meters across the projects, for example, is 23.</t>
+  </si>
+  <si>
+    <t>The minimum number of rooms in the project, for example, is 1.</t>
+  </si>
+  <si>
+    <t>The minimum number of bathrooms in the project, for example, is 1.</t>
+  </si>
+  <si>
+    <t>Maximum Number of bathrooms across the projects. Example: 4</t>
+  </si>
+  <si>
+    <t>The maximum size of the living area in square meters across the projects. Example: 19.76</t>
+  </si>
+  <si>
+    <t>The minimum size of the living area in square meters across the projects. Example: 15.78</t>
+  </si>
+  <si>
+    <t>Minimum Price for Sakani beneficiaries across the projects . Example: 246222.652</t>
+  </si>
+  <si>
+    <t>Maximum Price for Sakani beneficiaries across the projects. Example: 267922.798</t>
+  </si>
+  <si>
+    <t>Minimum Price for non-Sakani beneficiaries across the projects. Example: 301921</t>
+  </si>
+  <si>
+    <t>Maximum Price for non-Sakani beneficiaries across the projects. Example: 330190</t>
+  </si>
+  <si>
+    <t>Minimum Area of the apartment in square meters across the projects. Example: 149.1</t>
+  </si>
+  <si>
+    <t>Maximum Area of the apartment in square meters across the projects. Example: 152.5</t>
   </si>
 </sst>
 </file>
@@ -464,13 +464,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1114,7 +1126,7 @@
   <cols>
     <col min="2" max="2" width="10.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="77" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="77" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1127,7 +1139,7 @@
       <c r="C1" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>67</v>
       </c>
       <c r="E1" s="2" t="s">
@@ -1144,7 +1156,7 @@
       <c r="C2" t="s">
         <v>3</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="4" t="s">
         <v>35</v>
       </c>
       <c r="E2" t="s">
@@ -1161,7 +1173,7 @@
       <c r="C3" t="s">
         <v>4</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="4" t="s">
         <v>36</v>
       </c>
       <c r="E3" t="s">
@@ -1178,8 +1190,8 @@
       <c r="C4" t="s">
         <v>63</v>
       </c>
-      <c r="D4" t="s">
-        <v>115</v>
+      <c r="D4" s="4" t="s">
+        <v>95</v>
       </c>
       <c r="E4" t="s">
         <v>33</v>
@@ -1196,8 +1208,8 @@
       <c r="C5" t="s">
         <v>18</v>
       </c>
-      <c r="D5" t="s">
-        <v>123</v>
+      <c r="D5" s="4" t="s">
+        <v>103</v>
       </c>
       <c r="E5" t="s">
         <v>33</v>
@@ -1214,8 +1226,8 @@
       <c r="C6" t="s">
         <v>19</v>
       </c>
-      <c r="D6" t="s">
-        <v>122</v>
+      <c r="D6" s="4" t="s">
+        <v>102</v>
       </c>
       <c r="E6" t="s">
         <v>31</v>
@@ -1232,8 +1244,8 @@
       <c r="C7" t="s">
         <v>20</v>
       </c>
-      <c r="D7" t="s">
-        <v>121</v>
+      <c r="D7" s="4" t="s">
+        <v>101</v>
       </c>
       <c r="E7" t="s">
         <v>31</v>
@@ -1250,7 +1262,7 @@
       <c r="C8" t="s">
         <v>21</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="4" t="s">
         <v>54</v>
       </c>
       <c r="E8" t="s">
@@ -1268,8 +1280,8 @@
       <c r="C9" t="s">
         <v>22</v>
       </c>
-      <c r="D9" t="s">
-        <v>120</v>
+      <c r="D9" s="4" t="s">
+        <v>100</v>
       </c>
       <c r="E9" t="s">
         <v>31</v>
@@ -1286,8 +1298,8 @@
       <c r="C10" t="s">
         <v>23</v>
       </c>
-      <c r="D10" t="s">
-        <v>119</v>
+      <c r="D10" s="4" t="s">
+        <v>99</v>
       </c>
       <c r="E10" t="s">
         <v>33</v>
@@ -1304,8 +1316,8 @@
       <c r="C11" t="s">
         <v>24</v>
       </c>
-      <c r="D11" t="s">
-        <v>118</v>
+      <c r="D11" s="4" t="s">
+        <v>98</v>
       </c>
       <c r="E11" t="s">
         <v>33</v>
@@ -1322,8 +1334,8 @@
       <c r="C12" t="s">
         <v>25</v>
       </c>
-      <c r="D12" t="s">
-        <v>117</v>
+      <c r="D12" s="4" t="s">
+        <v>97</v>
       </c>
       <c r="E12" t="s">
         <v>33</v>
@@ -1340,8 +1352,8 @@
       <c r="C13" t="s">
         <v>26</v>
       </c>
-      <c r="D13" t="s">
-        <v>116</v>
+      <c r="D13" s="4" t="s">
+        <v>96</v>
       </c>
       <c r="E13" t="s">
         <v>33</v>
@@ -1357,7 +1369,7 @@
       <c r="C14" t="s">
         <v>4</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="4" t="s">
         <v>36</v>
       </c>
       <c r="E14" t="s">
@@ -1374,7 +1386,7 @@
       <c r="C15" t="s">
         <v>5</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="4" t="s">
         <v>37</v>
       </c>
       <c r="E15" t="s">
@@ -1391,7 +1403,7 @@
       <c r="C16" t="s">
         <v>6</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="4" t="s">
         <v>38</v>
       </c>
       <c r="E16" t="s">
@@ -1408,8 +1420,8 @@
       <c r="C17" t="s">
         <v>7</v>
       </c>
-      <c r="D17" t="s">
-        <v>113</v>
+      <c r="D17" s="4" t="s">
+        <v>93</v>
       </c>
       <c r="E17" t="s">
         <v>30</v>
@@ -1425,8 +1437,8 @@
       <c r="C18" t="s">
         <v>8</v>
       </c>
-      <c r="D18" t="s">
-        <v>114</v>
+      <c r="D18" s="4" t="s">
+        <v>94</v>
       </c>
       <c r="E18" t="s">
         <v>30</v>
@@ -1442,7 +1454,7 @@
       <c r="C19" t="s">
         <v>9</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" s="4" t="s">
         <v>41</v>
       </c>
       <c r="E19" t="s">
@@ -1459,7 +1471,7 @@
       <c r="C20" t="s">
         <v>12</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" s="4" t="s">
         <v>44</v>
       </c>
       <c r="E20" t="s">
@@ -1476,7 +1488,7 @@
       <c r="C21" t="s">
         <v>13</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D21" s="4" t="s">
         <v>45</v>
       </c>
       <c r="E21" t="s">
@@ -1493,7 +1505,7 @@
       <c r="C22" t="s">
         <v>14</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" s="4" t="s">
         <v>46</v>
       </c>
       <c r="E22" t="s">
@@ -1510,7 +1522,7 @@
       <c r="C23" t="s">
         <v>69</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" s="4" t="s">
         <v>42</v>
       </c>
       <c r="E23" t="s">
@@ -1527,7 +1539,7 @@
       <c r="C24" t="s">
         <v>70</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D24" s="4" t="s">
         <v>43</v>
       </c>
       <c r="E24" t="s">
@@ -1544,7 +1556,7 @@
       <c r="C25" t="s">
         <v>71</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D25" s="4" t="s">
         <v>47</v>
       </c>
       <c r="E25" t="s">
@@ -1561,8 +1573,8 @@
       <c r="C26" t="s">
         <v>72</v>
       </c>
-      <c r="D26" t="s">
-        <v>112</v>
+      <c r="D26" s="4" t="s">
+        <v>118</v>
       </c>
       <c r="E26" t="s">
         <v>33</v>
@@ -1578,8 +1590,8 @@
       <c r="C27" t="s">
         <v>73</v>
       </c>
-      <c r="D27" t="s">
-        <v>74</v>
+      <c r="D27" s="4" t="s">
+        <v>119</v>
       </c>
       <c r="E27" t="s">
         <v>33</v>
@@ -1593,10 +1605,10 @@
         <v>15</v>
       </c>
       <c r="C28" t="s">
-        <v>75</v>
-      </c>
-      <c r="D28" t="s">
-        <v>111</v>
+        <v>74</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>120</v>
       </c>
       <c r="E28" t="s">
         <v>33</v>
@@ -1610,50 +1622,50 @@
         <v>16</v>
       </c>
       <c r="C29" t="s">
+        <v>75</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="E29" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A30" s="5">
+        <v>1</v>
+      </c>
+      <c r="B30" s="5">
+        <v>17</v>
+      </c>
+      <c r="C30" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D30" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A31" s="5">
+        <v>1</v>
+      </c>
+      <c r="B31" s="5">
+        <v>18</v>
+      </c>
+      <c r="C31" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="E29" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>1</v>
-      </c>
-      <c r="B30">
-        <v>17</v>
-      </c>
-      <c r="C30" t="s">
-        <v>78</v>
-      </c>
-      <c r="D30" t="s">
-        <v>110</v>
-      </c>
-      <c r="E30" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>1</v>
-      </c>
-      <c r="B31">
-        <v>18</v>
-      </c>
-      <c r="C31" t="s">
-        <v>79</v>
-      </c>
-      <c r="D31" t="s">
-        <v>80</v>
-      </c>
-      <c r="E31" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D31" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>1</v>
       </c>
@@ -1662,16 +1674,16 @@
         <v>19</v>
       </c>
       <c r="C32" t="s">
-        <v>81</v>
-      </c>
-      <c r="D32" t="s">
-        <v>109</v>
+        <v>78</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>117</v>
       </c>
       <c r="E32" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>1</v>
       </c>
@@ -1680,10 +1692,10 @@
         <v>20</v>
       </c>
       <c r="C33" t="s">
-        <v>82</v>
-      </c>
-      <c r="D33" t="s">
-        <v>83</v>
+        <v>79</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>116</v>
       </c>
       <c r="E33" t="s">
         <v>33</v>
@@ -1700,8 +1712,8 @@
       <c r="C34" t="s">
         <v>19</v>
       </c>
-      <c r="D34" t="s">
-        <v>84</v>
+      <c r="D34" s="4" t="s">
+        <v>80</v>
       </c>
       <c r="E34" t="s">
         <v>31</v>
@@ -1716,10 +1728,10 @@
         <v>22</v>
       </c>
       <c r="C35" t="s">
-        <v>85</v>
-      </c>
-      <c r="D35" t="s">
-        <v>88</v>
+        <v>81</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>114</v>
       </c>
       <c r="E35" t="s">
         <v>31</v>
@@ -1734,10 +1746,10 @@
         <v>23</v>
       </c>
       <c r="C36" t="s">
-        <v>86</v>
-      </c>
-      <c r="D36" t="s">
-        <v>87</v>
+        <v>82</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>115</v>
       </c>
       <c r="E36" t="s">
         <v>31</v>
@@ -1754,7 +1766,7 @@
       <c r="C37" t="s">
         <v>21</v>
       </c>
-      <c r="D37" t="s">
+      <c r="D37" s="4" t="s">
         <v>54</v>
       </c>
       <c r="E37" t="s">
@@ -1770,10 +1782,10 @@
         <v>25</v>
       </c>
       <c r="C38" t="s">
-        <v>89</v>
-      </c>
-      <c r="D38" t="s">
-        <v>108</v>
+        <v>83</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>113</v>
       </c>
       <c r="E38" t="s">
         <v>31</v>
@@ -1788,16 +1800,16 @@
         <v>26</v>
       </c>
       <c r="C39" t="s">
-        <v>90</v>
-      </c>
-      <c r="D39" t="s">
-        <v>91</v>
+        <v>84</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>104</v>
       </c>
       <c r="E39" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>1</v>
       </c>
@@ -1806,16 +1818,16 @@
         <v>27</v>
       </c>
       <c r="C40" t="s">
-        <v>92</v>
-      </c>
-      <c r="D40" t="s">
-        <v>107</v>
+        <v>85</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>105</v>
       </c>
       <c r="E40" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>1</v>
       </c>
@@ -1824,16 +1836,16 @@
         <v>28</v>
       </c>
       <c r="C41" t="s">
-        <v>93</v>
-      </c>
-      <c r="D41" t="s">
-        <v>94</v>
+        <v>86</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>106</v>
       </c>
       <c r="E41" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>1</v>
       </c>
@@ -1842,16 +1854,16 @@
         <v>29</v>
       </c>
       <c r="C42" t="s">
-        <v>95</v>
-      </c>
-      <c r="D42" t="s">
-        <v>106</v>
+        <v>87</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>107</v>
       </c>
       <c r="E42" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>1</v>
       </c>
@@ -1860,16 +1872,16 @@
         <v>30</v>
       </c>
       <c r="C43" t="s">
-        <v>96</v>
-      </c>
-      <c r="D43" t="s">
-        <v>97</v>
+        <v>88</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>108</v>
       </c>
       <c r="E43" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>1</v>
       </c>
@@ -1878,16 +1890,16 @@
         <v>31</v>
       </c>
       <c r="C44" t="s">
-        <v>98</v>
-      </c>
-      <c r="D44" t="s">
-        <v>105</v>
+        <v>89</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>109</v>
       </c>
       <c r="E44" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>1</v>
       </c>
@@ -1896,16 +1908,16 @@
         <v>32</v>
       </c>
       <c r="C45" t="s">
-        <v>99</v>
-      </c>
-      <c r="D45" t="s">
-        <v>102</v>
+        <v>90</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>110</v>
       </c>
       <c r="E45" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>1</v>
       </c>
@@ -1914,16 +1926,16 @@
         <v>33</v>
       </c>
       <c r="C46" t="s">
-        <v>100</v>
-      </c>
-      <c r="D46" t="s">
-        <v>104</v>
+        <v>91</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>111</v>
       </c>
       <c r="E46" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>1</v>
       </c>
@@ -1932,10 +1944,10 @@
         <v>34</v>
       </c>
       <c r="C47" t="s">
-        <v>101</v>
-      </c>
-      <c r="D47" t="s">
-        <v>103</v>
+        <v>92</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>112</v>
       </c>
       <c r="E47" t="s">
         <v>33</v>
@@ -1952,7 +1964,7 @@
       <c r="C48" t="s">
         <v>29</v>
       </c>
-      <c r="D48" t="s">
+      <c r="D48" s="4" t="s">
         <v>62</v>
       </c>
       <c r="E48" t="s">
